--- a/docs/eval/golden-set.xlsx
+++ b/docs/eval/golden-set.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerom\ConferenceFinder\docs\eval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6A800D-EDCB-497B-AA56-FB1E4F36CBAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0045FB-F638-4026-BFDE-7740EB6AE98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="golden" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="334">
   <si>
     <t>id</t>
   </si>
@@ -242,9 +242,6 @@
     <t>2026-04-20</t>
   </si>
   <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
     <t>2025-03-31</t>
   </si>
   <si>
@@ -272,809 +269,797 @@
     <t>Dresden, Germany</t>
   </si>
   <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>2025-04-11</t>
+  </si>
+  <si>
+    <t>Prague, Czech Republic</t>
+  </si>
+  <si>
+    <t>conf_007</t>
+  </si>
+  <si>
+    <t>ICMF</t>
+  </si>
+  <si>
+    <t>열전달</t>
+  </si>
+  <si>
+    <t>2023-04-02</t>
+  </si>
+  <si>
+    <t>2023-04-07</t>
+  </si>
+  <si>
+    <t>Kobe International Conference Center, Kobe, Japan</t>
+  </si>
+  <si>
+    <t>http://www.jsmf.gr.jp/icmf2022/</t>
+  </si>
+  <si>
+    <t>conf_008</t>
+  </si>
+  <si>
+    <t>ITherm</t>
+  </si>
+  <si>
+    <t>https://www.ieee-itherm.net/</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>Orlando, United States</t>
+  </si>
+  <si>
+    <t>2025-05-27</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>Gaylord Texan Resort and Convention Center, Dallas, TX, USA</t>
+  </si>
+  <si>
+    <t>conf_009</t>
+  </si>
+  <si>
+    <t>ICC</t>
+  </si>
+  <si>
+    <t>International Cryocooler Conference</t>
+  </si>
+  <si>
+    <t>https://cryocooler.org/</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>Syracuse, New York, United States</t>
+  </si>
+  <si>
+    <t>2024-06-03</t>
+  </si>
+  <si>
+    <t>2024-06-06</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin, USA</t>
+  </si>
+  <si>
+    <t>conf_010</t>
+  </si>
+  <si>
+    <t>TPTPR</t>
+  </si>
+  <si>
+    <t>IIR Conference on Thermophysical Properties and Transfer Processes of Refrigerants</t>
+  </si>
+  <si>
+    <t>열물성/냉매</t>
+  </si>
+  <si>
+    <t>전세계</t>
+  </si>
+  <si>
+    <t>https://iifiir.org/en/iir-conferences-series</t>
+  </si>
+  <si>
+    <t>2025-06-15</t>
+  </si>
+  <si>
+    <t>2025-06-18</t>
+  </si>
+  <si>
+    <t>University of Maryland, College Park, MD, USA</t>
+  </si>
+  <si>
+    <t>https://ceee.umd.edu/tptpr2025</t>
+  </si>
+  <si>
+    <t>conf_011</t>
+  </si>
+  <si>
+    <t>ECOS</t>
+  </si>
+  <si>
+    <t>International Conference on Efficiency, Cost, Optmization, Simulation and Environmental Impact of Energy Systems</t>
+  </si>
+  <si>
+    <t>신재생</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>Constanța, Romania</t>
+  </si>
+  <si>
+    <t>https://ecos2026.insae.ro/</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>2025-07-04</t>
+  </si>
+  <si>
+    <t>Mines Paris - PSL, Paris, France</t>
+  </si>
+  <si>
+    <t>https://ecos2025.org/</t>
+  </si>
+  <si>
+    <t>conf_012</t>
+  </si>
+  <si>
+    <t>THERMINIC</t>
+  </si>
+  <si>
+    <t>International Workshop on Thermal Investigations of ICs and Systems</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>Berlin-Köpenick, Germany</t>
+  </si>
+  <si>
+    <t>2025-09-24</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>University Federico II Conference Center, Naples, Italy</t>
+  </si>
+  <si>
+    <t>conf_013</t>
+  </si>
+  <si>
+    <t>Vienna, Austria</t>
+  </si>
+  <si>
+    <t>https://hpc2026.org/</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>2023-05-18</t>
+  </si>
+  <si>
+    <t>Renaissance Chicago Downtown Hotel, Chicago, IL, USA</t>
+  </si>
+  <si>
+    <t>https://www.hpc2023.org/</t>
+  </si>
+  <si>
+    <t>conf_014</t>
+  </si>
+  <si>
+    <t>ICBCHT</t>
+  </si>
+  <si>
+    <t>International Conference On Boiling &amp; Condensation Heat Transfer</t>
+  </si>
+  <si>
+    <t>https://sites.mit.edu/icbcht12/</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>Cambridge, USA</t>
+  </si>
+  <si>
+    <t>2023-05-17</t>
+  </si>
+  <si>
+    <t>University of Edinburgh, Edinburgh, UK</t>
+  </si>
+  <si>
+    <t>https://icbcht11.eng.ed.ac.uk/</t>
+  </si>
+  <si>
+    <t>conf_015</t>
+  </si>
+  <si>
+    <t>ICCFD</t>
+  </si>
+  <si>
+    <t>International Conference on Computational Fluid Dynamics</t>
+  </si>
+  <si>
+    <t>유체역학</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>Milan, Italy</t>
+  </si>
+  <si>
+    <t>2024-07-14</t>
+  </si>
+  <si>
+    <t>2024-07-19</t>
+  </si>
+  <si>
+    <t>conf_016</t>
+  </si>
+  <si>
+    <t>IHTC</t>
+  </si>
+  <si>
+    <t>International Heat Transfer Conference</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>Rio de Janeiro, Brazil</t>
+  </si>
+  <si>
+    <t>https://ihtc18.org/</t>
+  </si>
+  <si>
+    <t>2023-08-14</t>
+  </si>
+  <si>
+    <t>2023-08-18</t>
+  </si>
+  <si>
+    <t>Cape Town International Convention Centre, Cape Town, South Africa</t>
+  </si>
+  <si>
+    <t>https://ihtc17.org/</t>
+  </si>
+  <si>
+    <t>conf_017</t>
+  </si>
+  <si>
+    <t>PRTEC</t>
+  </si>
+  <si>
+    <t>Pacific Rim Thermal Engineering Conference</t>
+  </si>
+  <si>
+    <t>2027-03-14</t>
+  </si>
+  <si>
+    <t>2027-03-18</t>
+  </si>
+  <si>
+    <t>Honolulu, USA</t>
+  </si>
+  <si>
+    <t>https://www.prtec2027.org/</t>
+  </si>
+  <si>
+    <t>2024-12-15</t>
+  </si>
+  <si>
+    <t>2024-12-19</t>
+  </si>
+  <si>
+    <t>Hawaii Convention Center, Honolulu, HI, USA</t>
+  </si>
+  <si>
+    <t>https://prtec2024.org/</t>
+  </si>
+  <si>
+    <t>conf_018</t>
+  </si>
+  <si>
+    <t>ICR</t>
+  </si>
+  <si>
+    <t>IIR International Congress of Refrigeration</t>
+  </si>
+  <si>
+    <t>2027-08-21</t>
+  </si>
+  <si>
+    <t>2027-08-27</t>
+  </si>
+  <si>
+    <t>Seoul, Republic of Korea</t>
+  </si>
+  <si>
+    <t>https://www.icr2027.org/</t>
+  </si>
+  <si>
+    <t>2023-08-21</t>
+  </si>
+  <si>
+    <t>2023-08-26</t>
+  </si>
+  <si>
+    <t>Palais des Congrès de Paris, Paris, France</t>
+  </si>
+  <si>
+    <t>https://www.icr2023.org/</t>
+  </si>
+  <si>
+    <t>conf_019</t>
+  </si>
+  <si>
+    <t>IIR Gustav Lorentzen Conference on Natural Refrigerants</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>Hamilton, New Zealand</t>
+  </si>
+  <si>
+    <t>2024-08-11</t>
+  </si>
+  <si>
+    <t>2024-08-14</t>
+  </si>
+  <si>
+    <t>https://ceee.umd.edu/gl2024</t>
+  </si>
+  <si>
+    <t>conf_020</t>
+  </si>
+  <si>
+    <t>ACRA</t>
+  </si>
+  <si>
+    <t>Asian Conference on Refrigeration and Air-conditioning</t>
+  </si>
+  <si>
+    <t>2026-05-17</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>Taichung, Taiwan</t>
+  </si>
+  <si>
+    <t>2024-04-21</t>
+  </si>
+  <si>
+    <t>2024-04-24</t>
+  </si>
+  <si>
+    <t>Ramada Plaza Hotel Jeju, Jeju, South Korea</t>
+  </si>
+  <si>
+    <t>https://www.acra2024.org/</t>
+  </si>
+  <si>
+    <t>conf_021</t>
+  </si>
+  <si>
+    <t>International Heat Pipe Conferences and Symposia</t>
+  </si>
+  <si>
+    <t>2026-05-24</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2025-01-29</t>
+  </si>
+  <si>
+    <t>2025-02-02</t>
+  </si>
+  <si>
+    <t>Pattaya, Thailand</t>
+  </si>
+  <si>
+    <t>https://www.heatpipethailand.com/</t>
+  </si>
+  <si>
+    <t>user_mo04ezfq</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>Building Simulation</t>
+  </si>
+  <si>
+    <t>https://ibpsa.org/</t>
+  </si>
+  <si>
+    <t>2027-08-29</t>
+  </si>
+  <si>
+    <t>2027-09-01</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>2025-08-24</t>
+  </si>
+  <si>
+    <t>2025-08-27</t>
+  </si>
+  <si>
+    <t>Brisbane, Australia</t>
+  </si>
+  <si>
+    <t>https://bs2025.org/</t>
+  </si>
+  <si>
+    <t>user_mo342nwc</t>
+  </si>
+  <si>
+    <t>MNHMT2027</t>
+  </si>
+  <si>
+    <t>Micro/Nanoscale Heat &amp; Mass Transfer International Conference</t>
+  </si>
+  <si>
+    <t>2027-01-09</t>
+  </si>
+  <si>
+    <t>2027-01-11</t>
+  </si>
+  <si>
+    <t>Napoli, Italy</t>
+  </si>
+  <si>
+    <t>2024-08-05</t>
+  </si>
+  <si>
+    <t>2024-08-07</t>
+  </si>
+  <si>
+    <t>University of Nottingham, Nottingham, UK</t>
+  </si>
+  <si>
+    <t>user_mo347qjj</t>
+  </si>
+  <si>
+    <t>Greensys</t>
+  </si>
+  <si>
+    <t>https://ishs.org/</t>
+  </si>
+  <si>
+    <t>2027-06-06</t>
+  </si>
+  <si>
+    <t>2027-06-10</t>
+  </si>
+  <si>
+    <t>Wageningen, Netherlands</t>
+  </si>
+  <si>
+    <t>2025-06-22</t>
+  </si>
+  <si>
+    <t>2025-06-27</t>
+  </si>
+  <si>
+    <t>University of Almería, Almería, Spain</t>
+  </si>
+  <si>
+    <t>https://www2.ual.es/greensys2025/</t>
+  </si>
+  <si>
+    <t>disc_mo51rke0v1</t>
+  </si>
+  <si>
+    <t>IWCB</t>
+  </si>
+  <si>
+    <t>열저장</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>Stuttgart, Germany</t>
+  </si>
+  <si>
+    <t>2024-09-23</t>
+  </si>
+  <si>
+    <t>2024-09-25</t>
+  </si>
+  <si>
+    <t>University of Stuttgart, Stuttgart, Germany</t>
+  </si>
+  <si>
+    <t>disc_mo520jhk7o</t>
+  </si>
+  <si>
+    <t>IRACC</t>
+  </si>
+  <si>
+    <t>https://docs.lib.purdue.edu/iracc/</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>West Lafayette, IN, United States</t>
+  </si>
+  <si>
+    <t>2024-07-15</t>
+  </si>
+  <si>
+    <t>2024-07-18</t>
+  </si>
+  <si>
+    <t>Purdue University, West Lafayette, IN, USA</t>
+  </si>
+  <si>
+    <t>disc_mo5d5wybn7</t>
+  </si>
+  <si>
+    <t>CDC</t>
+  </si>
+  <si>
+    <t>제어공학</t>
+  </si>
+  <si>
+    <t>2026-12-15</t>
+  </si>
+  <si>
+    <t>2026-12-18</t>
+  </si>
+  <si>
+    <t>Honolulu, Hawaii, USA</t>
+  </si>
+  <si>
+    <t>https://cdc2026.ieeecss.org/</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>https://cdc2025.ieeecss.org/</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>snapshot_date</t>
+  </si>
+  <si>
+    <t>active_version</t>
+  </si>
+  <si>
+    <t>v4</t>
+  </si>
+  <si>
+    <t>row_count</t>
+  </si>
+  <si>
+    <t>generator_version</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://www.ashrae.org/conferences</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.aseanhvacexpo.com/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ish.messefrankfurt.com/frankfurt/en.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.euroturbo.eu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.cryogenics-conference.eu/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>International Conference on Multiphase Flow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE The Intersociety Conference on Thermal and Thermomechanical Phenomena in Electronic Systems</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://iifiir.org/en/iir-conferences-series</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ecosinternationalsociety.org/</t>
+  </si>
+  <si>
+    <t>IEA Heat Pump Conference</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://heatpumpingtechnologies.org/about-hpt-tcp/iea-heat-pump-conference/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://therminic.eu/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.astfe.org/conferences/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IHPC&amp;S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ihpcs.org/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.ichmt.org/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://event.dlr.de/en/</t>
+  </si>
+  <si>
+    <t>IEEE Conference on Decision and Control</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>International Workshop on Carnot Batteries</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>International Refrigeration and Air Conditioning Conference at Purdue (Harrick Conference)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lab.kobe-u.ac.jp/eng-mfd/event.html</t>
+  </si>
+  <si>
+    <t>Vancouver, Canada</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>low</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>high</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.iir-gl-2026.net/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://sites.google.com/view/hvac-acra2026/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ihpcs.org/ihpcs2026/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ibpsa.org/conferences/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.ichmt.org/mnhmt-2027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.ishs.org/symposium/854</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://event.dlr.de/en/event/5th-international-workshop-on-carnot-batteries-iwcb/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://chpb.engineering.purdue.edu/herrick-conferences/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.ashrae.org/conferences/2026-winter-conference</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.hannovermesse.de/en</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.cryogenics-conference.eu/cryogenics2023/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.ieee-itherm.net</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.ichmt.org/mnhmt-2024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://iwcb2024.welcome-manager.de/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://cryocooler.org/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>https://www.cryogenics-conference.eu/cryogenics2027/</t>
-  </si>
-  <si>
-    <t>2025-04-07</t>
-  </si>
-  <si>
-    <t>2025-04-11</t>
-  </si>
-  <si>
-    <t>Prague, Czech Republic</t>
-  </si>
-  <si>
-    <t>conf_007</t>
-  </si>
-  <si>
-    <t>ICMF</t>
-  </si>
-  <si>
-    <t>열전달</t>
-  </si>
-  <si>
-    <t>2023-04-02</t>
-  </si>
-  <si>
-    <t>2023-04-07</t>
-  </si>
-  <si>
-    <t>Kobe International Conference Center, Kobe, Japan</t>
-  </si>
-  <si>
-    <t>http://www.jsmf.gr.jp/icmf2022/</t>
-  </si>
-  <si>
-    <t>conf_008</t>
-  </si>
-  <si>
-    <t>ITherm</t>
-  </si>
-  <si>
-    <t>https://www.ieee-itherm.net/</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>Orlando, United States</t>
-  </si>
-  <si>
-    <t>2025-05-27</t>
-  </si>
-  <si>
-    <t>2025-05-30</t>
-  </si>
-  <si>
-    <t>Gaylord Texan Resort and Convention Center, Dallas, TX, USA</t>
-  </si>
-  <si>
-    <t>conf_009</t>
-  </si>
-  <si>
-    <t>ICC</t>
-  </si>
-  <si>
-    <t>International Cryocooler Conference</t>
-  </si>
-  <si>
-    <t>https://cryocooler.org/</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>Syracuse, New York, United States</t>
-  </si>
-  <si>
-    <t>2024-06-03</t>
-  </si>
-  <si>
-    <t>2024-06-06</t>
-  </si>
-  <si>
-    <t>Madison, Wisconsin, USA</t>
-  </si>
-  <si>
-    <t>conf_010</t>
-  </si>
-  <si>
-    <t>TPTPR</t>
-  </si>
-  <si>
-    <t>IIR Conference on Thermophysical Properties and Transfer Processes of Refrigerants</t>
-  </si>
-  <si>
-    <t>열물성/냉매</t>
-  </si>
-  <si>
-    <t>전세계</t>
-  </si>
-  <si>
-    <t>https://iifiir.org/en/iir-conferences-series</t>
-  </si>
-  <si>
-    <t>2025-06-15</t>
-  </si>
-  <si>
-    <t>2025-06-18</t>
-  </si>
-  <si>
-    <t>University of Maryland, College Park, MD, USA</t>
-  </si>
-  <si>
-    <t>https://ceee.umd.edu/tptpr2025</t>
-  </si>
-  <si>
-    <t>conf_011</t>
-  </si>
-  <si>
-    <t>ECOS</t>
-  </si>
-  <si>
-    <t>International Conference on Efficiency, Cost, Optmization, Simulation and Environmental Impact of Energy Systems</t>
-  </si>
-  <si>
-    <t>신재생</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>Constanța, Romania</t>
-  </si>
-  <si>
-    <t>https://ecos2026.insae.ro/</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>2025-07-04</t>
-  </si>
-  <si>
-    <t>Mines Paris - PSL, Paris, France</t>
-  </si>
-  <si>
-    <t>https://ecos2025.org/</t>
-  </si>
-  <si>
-    <t>conf_012</t>
-  </si>
-  <si>
-    <t>THERMINIC</t>
-  </si>
-  <si>
-    <t>International Workshop on Thermal Investigations of ICs and Systems</t>
-  </si>
-  <si>
-    <t>2026-09-16</t>
-  </si>
-  <si>
-    <t>2026-09-18</t>
-  </si>
-  <si>
-    <t>Berlin-Köpenick, Germany</t>
-  </si>
-  <si>
-    <t>2025-09-24</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>University Federico II Conference Center, Naples, Italy</t>
-  </si>
-  <si>
-    <t>https://therminic2025.eu/</t>
-  </si>
-  <si>
-    <t>conf_013</t>
-  </si>
-  <si>
-    <t>Vienna, Austria</t>
-  </si>
-  <si>
-    <t>https://hpc2026.org/</t>
-  </si>
-  <si>
-    <t>2023-05-15</t>
-  </si>
-  <si>
-    <t>2023-05-18</t>
-  </si>
-  <si>
-    <t>Renaissance Chicago Downtown Hotel, Chicago, IL, USA</t>
-  </si>
-  <si>
-    <t>https://www.hpc2023.org/</t>
-  </si>
-  <si>
-    <t>conf_014</t>
-  </si>
-  <si>
-    <t>ICBCHT</t>
-  </si>
-  <si>
-    <t>International Conference On Boiling &amp; Condensation Heat Transfer</t>
-  </si>
-  <si>
-    <t>https://sites.mit.edu/icbcht12/</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>Cambridge, USA</t>
-  </si>
-  <si>
-    <t>2023-05-17</t>
-  </si>
-  <si>
-    <t>University of Edinburgh, Edinburgh, UK</t>
-  </si>
-  <si>
-    <t>https://icbcht11.eng.ed.ac.uk/</t>
-  </si>
-  <si>
-    <t>conf_015</t>
-  </si>
-  <si>
-    <t>ICCFD</t>
-  </si>
-  <si>
-    <t>International Conference on Computational Fluid Dynamics</t>
-  </si>
-  <si>
-    <t>유체역학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>https://www.iccfd.org/</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>Milan, Italy</t>
-  </si>
-  <si>
-    <t>2024-07-14</t>
-  </si>
-  <si>
-    <t>2024-07-19</t>
-  </si>
-  <si>
-    <t>https://www.iccfd.org/iccfd12/</t>
-  </si>
-  <si>
-    <t>conf_016</t>
-  </si>
-  <si>
-    <t>IHTC</t>
-  </si>
-  <si>
-    <t>International Heat Transfer Conference</t>
-  </si>
-  <si>
-    <t>2026-08-02</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>Rio de Janeiro, Brazil</t>
-  </si>
-  <si>
-    <t>https://ihtc18.org/</t>
-  </si>
-  <si>
-    <t>2023-08-14</t>
-  </si>
-  <si>
-    <t>2023-08-18</t>
-  </si>
-  <si>
-    <t>Cape Town International Convention Centre, Cape Town, South Africa</t>
-  </si>
-  <si>
-    <t>https://ihtc17.org/</t>
-  </si>
-  <si>
-    <t>conf_017</t>
-  </si>
-  <si>
-    <t>PRTEC</t>
-  </si>
-  <si>
-    <t>Pacific Rim Thermal Engineering Conference</t>
-  </si>
-  <si>
-    <t>2027-03-14</t>
-  </si>
-  <si>
-    <t>2027-03-18</t>
-  </si>
-  <si>
-    <t>Honolulu, USA</t>
-  </si>
-  <si>
-    <t>https://www.prtec2027.org/</t>
-  </si>
-  <si>
-    <t>2024-12-15</t>
-  </si>
-  <si>
-    <t>2024-12-19</t>
-  </si>
-  <si>
-    <t>Hawaii Convention Center, Honolulu, HI, USA</t>
-  </si>
-  <si>
-    <t>https://prtec2024.org/</t>
-  </si>
-  <si>
-    <t>conf_018</t>
-  </si>
-  <si>
-    <t>ICR</t>
-  </si>
-  <si>
-    <t>IIR International Congress of Refrigeration</t>
-  </si>
-  <si>
-    <t>2027-08-21</t>
-  </si>
-  <si>
-    <t>2027-08-27</t>
-  </si>
-  <si>
-    <t>Seoul, Republic of Korea</t>
-  </si>
-  <si>
-    <t>https://www.icr2027.org/</t>
-  </si>
-  <si>
-    <t>2023-08-21</t>
-  </si>
-  <si>
-    <t>2023-08-26</t>
-  </si>
-  <si>
-    <t>Palais des Congrès de Paris, Paris, France</t>
-  </si>
-  <si>
-    <t>https://www.icr2023.org/</t>
-  </si>
-  <si>
-    <t>conf_019</t>
-  </si>
-  <si>
-    <t>IIR Gustav Lorentzen Conference on Natural Refrigerants</t>
-  </si>
-  <si>
-    <t>2026-08-23</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>Hamilton, New Zealand</t>
-  </si>
-  <si>
-    <t>2024-08-11</t>
-  </si>
-  <si>
-    <t>2024-08-14</t>
-  </si>
-  <si>
-    <t>https://ceee.umd.edu/gl2024</t>
-  </si>
-  <si>
-    <t>conf_020</t>
-  </si>
-  <si>
-    <t>ACRA</t>
-  </si>
-  <si>
-    <t>Asian Conference on Refrigeration and Air-conditioning</t>
-  </si>
-  <si>
-    <t>2026-05-17</t>
-  </si>
-  <si>
-    <t>2026-05-20</t>
-  </si>
-  <si>
-    <t>Taichung, Taiwan</t>
-  </si>
-  <si>
-    <t>2024-04-21</t>
-  </si>
-  <si>
-    <t>2024-04-24</t>
-  </si>
-  <si>
-    <t>Ramada Plaza Hotel Jeju, Jeju, South Korea</t>
-  </si>
-  <si>
-    <t>https://www.acra2024.org/</t>
-  </si>
-  <si>
-    <t>conf_021</t>
-  </si>
-  <si>
-    <t>International Heat Pipe Conferences and Symposia</t>
-  </si>
-  <si>
-    <t>2026-05-24</t>
-  </si>
-  <si>
-    <t>2026-05-28</t>
-  </si>
-  <si>
-    <t>2025-01-29</t>
-  </si>
-  <si>
-    <t>2025-02-02</t>
-  </si>
-  <si>
-    <t>Pattaya, Thailand</t>
-  </si>
-  <si>
-    <t>https://www.heatpipethailand.com/</t>
-  </si>
-  <si>
-    <t>user_mo04ezfq</t>
-  </si>
-  <si>
-    <t>BS</t>
-  </si>
-  <si>
-    <t>Building Simulation</t>
-  </si>
-  <si>
-    <t>https://ibpsa.org/</t>
-  </si>
-  <si>
-    <t>2027-08-29</t>
-  </si>
-  <si>
-    <t>2027-09-01</t>
-  </si>
-  <si>
-    <t>medium</t>
-  </si>
-  <si>
-    <t>2025-08-24</t>
-  </si>
-  <si>
-    <t>2025-08-27</t>
-  </si>
-  <si>
-    <t>Brisbane, Australia</t>
-  </si>
-  <si>
-    <t>https://bs2025.org/</t>
-  </si>
-  <si>
-    <t>user_mo342nwc</t>
-  </si>
-  <si>
-    <t>MNHMT2027</t>
-  </si>
-  <si>
-    <t>Micro/Nanoscale Heat &amp; Mass Transfer International Conference</t>
-  </si>
-  <si>
-    <t>2027-01-09</t>
-  </si>
-  <si>
-    <t>2027-01-11</t>
-  </si>
-  <si>
-    <t>Napoli, Italy</t>
-  </si>
-  <si>
-    <t>2024-08-05</t>
-  </si>
-  <si>
-    <t>2024-08-07</t>
-  </si>
-  <si>
-    <t>University of Nottingham, Nottingham, UK</t>
-  </si>
-  <si>
-    <t>user_mo347qjj</t>
-  </si>
-  <si>
-    <t>Greensys</t>
-  </si>
-  <si>
-    <t>https://ishs.org/</t>
-  </si>
-  <si>
-    <t>2027-06-06</t>
-  </si>
-  <si>
-    <t>2027-06-10</t>
-  </si>
-  <si>
-    <t>Wageningen, Netherlands</t>
-  </si>
-  <si>
-    <t>2025-06-22</t>
-  </si>
-  <si>
-    <t>2025-06-27</t>
-  </si>
-  <si>
-    <t>University of Almería, Almería, Spain</t>
-  </si>
-  <si>
-    <t>https://www2.ual.es/greensys2025/</t>
-  </si>
-  <si>
-    <t>disc_mo51rke0v1</t>
-  </si>
-  <si>
-    <t>IWCB</t>
-  </si>
-  <si>
-    <t>열저장</t>
-  </si>
-  <si>
-    <t>2026-09-21</t>
-  </si>
-  <si>
-    <t>2026-09-23</t>
-  </si>
-  <si>
-    <t>Stuttgart, Germany</t>
-  </si>
-  <si>
-    <t>2024-09-23</t>
-  </si>
-  <si>
-    <t>2024-09-25</t>
-  </si>
-  <si>
-    <t>University of Stuttgart, Stuttgart, Germany</t>
-  </si>
-  <si>
-    <t>disc_mo520jhk7o</t>
-  </si>
-  <si>
-    <t>IRACC</t>
-  </si>
-  <si>
-    <t>https://docs.lib.purdue.edu/iracc/</t>
-  </si>
-  <si>
-    <t>2026-07-12</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>West Lafayette, IN, United States</t>
-  </si>
-  <si>
-    <t>2024-07-15</t>
-  </si>
-  <si>
-    <t>2024-07-18</t>
-  </si>
-  <si>
-    <t>Purdue University, West Lafayette, IN, USA</t>
-  </si>
-  <si>
-    <t>disc_mo5d5wybn7</t>
-  </si>
-  <si>
-    <t>CDC</t>
-  </si>
-  <si>
-    <t>제어공학</t>
-  </si>
-  <si>
-    <t>2026-12-15</t>
-  </si>
-  <si>
-    <t>2026-12-18</t>
-  </si>
-  <si>
-    <t>Honolulu, Hawaii, USA</t>
-  </si>
-  <si>
-    <t>https://cdc2026.ieeecss.org/</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>https://cdc2025.ieeecss.org/</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>snapshot_date</t>
-  </si>
-  <si>
-    <t>active_version</t>
-  </si>
-  <si>
-    <t>v4</t>
-  </si>
-  <si>
-    <t>row_count</t>
-  </si>
-  <si>
-    <t>generator_version</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>https://www.ashrae.org/conferences</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.aseanhvacexpo.com/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ish.messefrankfurt.com/frankfurt/en.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.euroturbo.eu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.cryogenics-conference.eu/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>International Conference on Multiphase Flow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IEEE The Intersociety Conference on Thermal and Thermomechanical Phenomena in Electronic Systems</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://iifiir.org/en/iir-conferences-series</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ecosinternationalsociety.org/</t>
-  </si>
-  <si>
-    <t>IEA Heat Pump Conference</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://heatpumpingtechnologies.org/about-hpt-tcp/iea-heat-pump-conference/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://therminic.eu/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.astfe.org/conferences/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IHPC&amp;S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ihpcs.org/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.ichmt.org/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://event.dlr.de/en/</t>
-  </si>
-  <si>
-    <t>IEEE Conference on Decision and Control</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>International Workshop on Carnot Batteries</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>International Refrigeration and Air Conditioning Conference at Purdue (Harrick Conference)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.lab.kobe-u.ac.jp/eng-mfd/event.html</t>
-  </si>
-  <si>
-    <t>Vancouver, Canada</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>low</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>high</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://iccfd13.polimi.it</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.iir-gl-2026.net/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://sites.google.com/view/hvac-acra2026/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ihpcs.org/ihpcs2026/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ibpsa.org/conferences/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.ichmt.org/mnhmt-2027</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.ishs.org/symposium/854</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://event.dlr.de/en/event/5th-international-workshop-on-carnot-batteries-iwcb/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://chpb.engineering.purdue.edu/herrick-conferences/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.ashrae.org/conferences/2026-winter-conference</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.hannovermesse.de/en</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.cryogenics-conference.eu/cryogenics2023/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.ieee-itherm.net</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.ichmt.org/mnhmt-2024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://iwcb2024.welcome-manager.de/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://therminic2026.eu/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://cryocooler.org/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1607,7 +1592,7 @@
         <v>29</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="K2" t="s">
         <v>25</v>
@@ -1640,7 +1625,7 @@
         <v>37</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="V2" t="s">
         <v>25</v>
@@ -1681,7 +1666,7 @@
         <v>42</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="K3" t="s">
         <v>25</v>
@@ -1696,7 +1681,7 @@
         <v>25</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="P3" t="s">
         <v>25</v>
@@ -1714,7 +1699,7 @@
         <v>45</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="V3" t="s">
         <v>25</v>
@@ -1755,7 +1740,7 @@
         <v>49</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="K4" t="s">
         <v>25</v>
@@ -1770,10 +1755,10 @@
         <v>53</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="P4" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1829,7 +1814,7 @@
         <v>49</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="K5" t="s">
         <v>25</v>
@@ -1903,22 +1888,13 @@
         <v>49</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="K6" t="s">
         <v>25</v>
       </c>
-      <c r="L6" t="s">
-        <v>72</v>
-      </c>
-      <c r="M6" t="s">
-        <v>73</v>
-      </c>
-      <c r="N6" t="s">
-        <v>67</v>
-      </c>
       <c r="O6" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="P6" t="s">
         <v>34</v>
@@ -1927,16 +1903,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="s">
+        <v>73</v>
+      </c>
+      <c r="S6" t="s">
         <v>74</v>
-      </c>
-      <c r="S6" t="s">
-        <v>75</v>
       </c>
       <c r="T6" t="s">
         <v>67</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="V6" t="s">
         <v>25</v>
@@ -1950,13 +1926,13 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
         <v>76</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1965,7 +1941,7 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1977,22 +1953,22 @@
         <v>49</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="K7" t="s">
+        <v>78</v>
+      </c>
+      <c r="L7" t="s">
         <v>79</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>80</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>81</v>
       </c>
-      <c r="N7" t="s">
-        <v>82</v>
-      </c>
-      <c r="O7" t="s">
-        <v>83</v>
+      <c r="O7" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="P7" t="s">
         <v>34</v>
@@ -2001,16 +1977,16 @@
         <v>0</v>
       </c>
       <c r="R7" t="s">
+        <v>82</v>
+      </c>
+      <c r="S7" t="s">
+        <v>83</v>
+      </c>
+      <c r="T7" t="s">
         <v>84</v>
       </c>
-      <c r="S7" t="s">
-        <v>85</v>
-      </c>
-      <c r="T7" t="s">
-        <v>86</v>
-      </c>
       <c r="U7" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="V7" t="s">
         <v>25</v>
@@ -2024,13 +2000,13 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2039,7 +2015,7 @@
         <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -2063,28 +2039,28 @@
         <v>25</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="O8" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="P8" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="Q8">
         <v>0</v>
       </c>
       <c r="R8" t="s">
+        <v>88</v>
+      </c>
+      <c r="S8" t="s">
+        <v>89</v>
+      </c>
+      <c r="T8" t="s">
         <v>90</v>
       </c>
-      <c r="S8" t="s">
+      <c r="U8" t="s">
         <v>91</v>
-      </c>
-      <c r="T8" t="s">
-        <v>92</v>
-      </c>
-      <c r="U8" t="s">
-        <v>93</v>
       </c>
       <c r="V8" t="s">
         <v>25</v>
@@ -2098,13 +2074,13 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -2113,7 +2089,7 @@
         <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2125,22 +2101,22 @@
         <v>29</v>
       </c>
       <c r="J9" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" t="s">
+        <v>95</v>
+      </c>
+      <c r="M9" t="s">
         <v>96</v>
       </c>
-      <c r="K9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
         <v>97</v>
       </c>
-      <c r="M9" t="s">
-        <v>98</v>
-      </c>
-      <c r="N9" t="s">
-        <v>99</v>
-      </c>
       <c r="O9" s="1" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="P9" t="s">
         <v>34</v>
@@ -2149,16 +2125,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="s">
+        <v>98</v>
+      </c>
+      <c r="S9" t="s">
+        <v>99</v>
+      </c>
+      <c r="T9" t="s">
         <v>100</v>
       </c>
-      <c r="S9" t="s">
-        <v>101</v>
-      </c>
-      <c r="T9" t="s">
-        <v>102</v>
-      </c>
       <c r="U9" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="V9" t="s">
         <v>25</v>
@@ -2172,13 +2148,13 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" t="s">
         <v>103</v>
-      </c>
-      <c r="B10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" t="s">
-        <v>105</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -2187,7 +2163,7 @@
         <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -2199,22 +2175,22 @@
         <v>29</v>
       </c>
       <c r="J10" t="s">
+        <v>104</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>105</v>
+      </c>
+      <c r="M10" t="s">
         <v>106</v>
       </c>
-      <c r="K10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="N10" t="s">
         <v>107</v>
       </c>
-      <c r="M10" t="s">
-        <v>108</v>
-      </c>
-      <c r="N10" t="s">
-        <v>109</v>
-      </c>
       <c r="O10" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="P10" t="s">
         <v>34</v>
@@ -2223,16 +2199,16 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
+        <v>108</v>
+      </c>
+      <c r="S10" t="s">
+        <v>109</v>
+      </c>
+      <c r="T10" t="s">
         <v>110</v>
       </c>
-      <c r="S10" t="s">
-        <v>111</v>
-      </c>
-      <c r="T10" t="s">
-        <v>112</v>
-      </c>
       <c r="U10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="V10" t="s">
         <v>25</v>
@@ -2246,13 +2222,13 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" t="s">
         <v>113</v>
-      </c>
-      <c r="B11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" t="s">
-        <v>115</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -2261,7 +2237,7 @@
         <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G11">
         <v>4</v>
@@ -2270,43 +2246,43 @@
         <v>4</v>
       </c>
       <c r="I11" t="s">
+        <v>115</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11" t="s">
         <v>117</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="K11" t="s">
-        <v>25</v>
-      </c>
-      <c r="L11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" t="s">
-        <v>25</v>
-      </c>
-      <c r="O11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P11" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
+        <v>118</v>
+      </c>
+      <c r="T11" t="s">
         <v>119</v>
       </c>
-      <c r="S11" t="s">
+      <c r="U11" t="s">
         <v>120</v>
-      </c>
-      <c r="T11" t="s">
-        <v>121</v>
-      </c>
-      <c r="U11" t="s">
-        <v>122</v>
       </c>
       <c r="V11" t="s">
         <v>25</v>
@@ -2320,13 +2296,13 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" t="s">
         <v>123</v>
-      </c>
-      <c r="B12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" t="s">
-        <v>125</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -2335,7 +2311,7 @@
         <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -2344,43 +2320,43 @@
         <v>5</v>
       </c>
       <c r="I12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J12" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K12" t="s">
         <v>25</v>
       </c>
       <c r="L12" t="s">
+        <v>125</v>
+      </c>
+      <c r="M12" t="s">
+        <v>126</v>
+      </c>
+      <c r="N12" t="s">
         <v>127</v>
       </c>
-      <c r="M12" t="s">
+      <c r="O12" t="s">
         <v>128</v>
       </c>
-      <c r="N12" t="s">
+      <c r="P12" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
         <v>129</v>
       </c>
-      <c r="O12" t="s">
+      <c r="S12" t="s">
         <v>130</v>
       </c>
-      <c r="P12" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12" t="s">
+      <c r="T12" t="s">
         <v>131</v>
       </c>
-      <c r="S12" t="s">
+      <c r="U12" t="s">
         <v>132</v>
-      </c>
-      <c r="T12" t="s">
-        <v>133</v>
-      </c>
-      <c r="U12" t="s">
-        <v>134</v>
       </c>
       <c r="V12" t="s">
         <v>25</v>
@@ -2394,13 +2370,13 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" t="s">
         <v>135</v>
-      </c>
-      <c r="B13" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" t="s">
-        <v>137</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -2409,7 +2385,7 @@
         <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2421,22 +2397,22 @@
         <v>49</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="K13" t="s">
         <v>25</v>
       </c>
       <c r="L13" t="s">
+        <v>136</v>
+      </c>
+      <c r="M13" t="s">
+        <v>137</v>
+      </c>
+      <c r="N13" t="s">
         <v>138</v>
       </c>
-      <c r="M13" t="s">
-        <v>139</v>
-      </c>
-      <c r="N13" t="s">
-        <v>140</v>
-      </c>
       <c r="O13" s="1" t="s">
-        <v>337</v>
+        <v>304</v>
       </c>
       <c r="P13" t="s">
         <v>34</v>
@@ -2445,16 +2421,16 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
+        <v>139</v>
+      </c>
+      <c r="S13" t="s">
+        <v>140</v>
+      </c>
+      <c r="T13" t="s">
         <v>141</v>
       </c>
-      <c r="S13" t="s">
-        <v>142</v>
-      </c>
-      <c r="T13" t="s">
-        <v>143</v>
-      </c>
-      <c r="U13" t="s">
-        <v>144</v>
+      <c r="U13" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="V13" t="s">
         <v>25</v>
@@ -2468,13 +2444,13 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B14" t="s">
         <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -2492,25 +2468,25 @@
         <v>4</v>
       </c>
       <c r="I14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="K14" t="s">
         <v>25</v>
       </c>
       <c r="L14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N14" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O14" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="P14" t="s">
         <v>34</v>
@@ -2519,16 +2495,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="s">
+        <v>145</v>
+      </c>
+      <c r="S14" t="s">
+        <v>146</v>
+      </c>
+      <c r="T14" t="s">
+        <v>147</v>
+      </c>
+      <c r="U14" t="s">
         <v>148</v>
-      </c>
-      <c r="S14" t="s">
-        <v>149</v>
-      </c>
-      <c r="T14" t="s">
-        <v>150</v>
-      </c>
-      <c r="U14" t="s">
-        <v>151</v>
       </c>
       <c r="V14" t="s">
         <v>25</v>
@@ -2542,13 +2518,13 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -2557,7 +2533,7 @@
         <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -2566,23 +2542,23 @@
         <v>3</v>
       </c>
       <c r="I15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" t="s">
         <v>25</v>
       </c>
       <c r="L15" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="M15" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="N15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O15" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P15" t="s">
         <v>34</v>
@@ -2591,16 +2567,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="S15" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="T15" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="U15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="V15" t="s">
         <v>25</v>
@@ -2614,13 +2590,13 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C16" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -2629,7 +2605,7 @@
         <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -2638,25 +2614,25 @@
         <v>5</v>
       </c>
       <c r="I16" t="s">
-        <v>117</v>
-      </c>
-      <c r="J16" t="s">
-        <v>166</v>
+        <v>115</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
       </c>
       <c r="L16" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="M16" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N16" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="P16" t="s">
         <v>34</v>
@@ -2665,16 +2641,16 @@
         <v>0</v>
       </c>
       <c r="R16" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="S16" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="T16" t="s">
-        <v>92</v>
-      </c>
-      <c r="U16" t="s">
-        <v>172</v>
+        <v>90</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="V16" t="s">
         <v>25</v>
@@ -2688,13 +2664,13 @@
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B17" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C17" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -2703,7 +2679,7 @@
         <v>27</v>
       </c>
       <c r="F17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G17">
         <v>4</v>
@@ -2712,25 +2688,25 @@
         <v>5</v>
       </c>
       <c r="I17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="K17" t="s">
         <v>25</v>
       </c>
       <c r="L17" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="M17" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="N17" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="O17" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="P17" t="s">
         <v>34</v>
@@ -2739,16 +2715,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="S17" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="T17" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="U17" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="V17" t="s">
         <v>25</v>
@@ -2762,13 +2738,13 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B18" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C18" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -2777,7 +2753,7 @@
         <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G18">
         <v>4</v>
@@ -2795,16 +2771,16 @@
         <v>25</v>
       </c>
       <c r="L18" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="M18" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="N18" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O18" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="P18" t="s">
         <v>34</v>
@@ -2813,16 +2789,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="S18" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="T18" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="U18" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="V18" t="s">
         <v>25</v>
@@ -2836,13 +2812,13 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -2860,25 +2836,25 @@
         <v>6</v>
       </c>
       <c r="I19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L19" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="M19" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="N19" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="O19" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="P19" t="s">
         <v>34</v>
@@ -2887,16 +2863,16 @@
         <v>0</v>
       </c>
       <c r="R19" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="S19" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="T19" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="U19" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="V19" t="s">
         <v>25</v>
@@ -2910,13 +2886,13 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s">
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -2925,7 +2901,7 @@
         <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -2934,43 +2910,43 @@
         <v>4</v>
       </c>
       <c r="I20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L20" t="s">
+        <v>203</v>
+      </c>
+      <c r="M20" t="s">
+        <v>204</v>
+      </c>
+      <c r="N20" t="s">
+        <v>205</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="P20" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20" t="s">
+        <v>206</v>
+      </c>
+      <c r="S20" t="s">
+        <v>207</v>
+      </c>
+      <c r="T20" t="s">
+        <v>119</v>
+      </c>
+      <c r="U20" t="s">
         <v>208</v>
-      </c>
-      <c r="M20" t="s">
-        <v>209</v>
-      </c>
-      <c r="N20" t="s">
-        <v>210</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="P20" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20" t="s">
-        <v>211</v>
-      </c>
-      <c r="S20" t="s">
-        <v>212</v>
-      </c>
-      <c r="T20" t="s">
-        <v>121</v>
-      </c>
-      <c r="U20" t="s">
-        <v>213</v>
       </c>
       <c r="V20" t="s">
         <v>25</v>
@@ -2984,13 +2960,13 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C21" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -3014,16 +2990,16 @@
         <v>25</v>
       </c>
       <c r="L21" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="N21" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="P21" t="s">
         <v>34</v>
@@ -3032,16 +3008,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="S21" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="T21" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="U21" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="V21" t="s">
         <v>25</v>
@@ -3055,13 +3031,13 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -3070,7 +3046,7 @@
         <v>27</v>
       </c>
       <c r="F22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -3079,25 +3055,25 @@
         <v>5</v>
       </c>
       <c r="I22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="K22" t="s">
         <v>25</v>
       </c>
       <c r="L22" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="N22" t="s">
         <v>63</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="P22" t="s">
         <v>34</v>
@@ -3106,16 +3082,16 @@
         <v>0</v>
       </c>
       <c r="R22" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="S22" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="T22" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="U22" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="V22" t="s">
         <v>25</v>
@@ -3129,13 +3105,13 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C23" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -3153,43 +3129,43 @@
         <v>4</v>
       </c>
       <c r="I23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J23" t="s">
+        <v>230</v>
+      </c>
+      <c r="K23" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" t="s">
+        <v>231</v>
+      </c>
+      <c r="M23" t="s">
+        <v>232</v>
+      </c>
+      <c r="N23" t="s">
+        <v>143</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="P23" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23" t="s">
+        <v>234</v>
+      </c>
+      <c r="S23" t="s">
         <v>235</v>
       </c>
-      <c r="K23" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" t="s">
+      <c r="T23" t="s">
         <v>236</v>
       </c>
-      <c r="M23" t="s">
+      <c r="U23" t="s">
         <v>237</v>
-      </c>
-      <c r="N23" t="s">
-        <v>146</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="P23" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23" t="s">
-        <v>239</v>
-      </c>
-      <c r="S23" t="s">
-        <v>240</v>
-      </c>
-      <c r="T23" t="s">
-        <v>241</v>
-      </c>
-      <c r="U23" t="s">
-        <v>242</v>
       </c>
       <c r="V23" t="s">
         <v>25</v>
@@ -3203,13 +3179,13 @@
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C24" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -3218,7 +3194,7 @@
         <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G24">
         <v>3</v>
@@ -3227,25 +3203,25 @@
         <v>3</v>
       </c>
       <c r="I24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="K24" t="s">
         <v>25</v>
       </c>
       <c r="L24" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="P24" t="s">
         <v>34</v>
@@ -3254,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="S24" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="T24" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="V24" t="s">
         <v>25</v>
@@ -3277,13 +3253,13 @@
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s">
         <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -3301,25 +3277,25 @@
         <v>5</v>
       </c>
       <c r="I25" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J25" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="K25" t="s">
         <v>25</v>
       </c>
       <c r="L25" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="N25" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="P25" t="s">
         <v>34</v>
@@ -3328,16 +3304,16 @@
         <v>0</v>
       </c>
       <c r="R25" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="S25" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="T25" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="U25" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="V25" t="s">
         <v>25</v>
@@ -3351,13 +3327,13 @@
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C26" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -3366,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -3378,22 +3354,22 @@
         <v>49</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="K26" t="s">
         <v>25</v>
       </c>
       <c r="L26" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="P26" t="s">
         <v>34</v>
@@ -3402,16 +3378,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="S26" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="T26" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="V26" t="s">
         <v>25</v>
@@ -3425,13 +3401,13 @@
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C27" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -3449,25 +3425,25 @@
         <v>5</v>
       </c>
       <c r="I27" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J27" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="K27" t="s">
         <v>25</v>
       </c>
       <c r="L27" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="N27" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P27" t="s">
         <v>34</v>
@@ -3476,16 +3452,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="S27" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="T27" t="s">
-        <v>279</v>
-      </c>
-      <c r="U27" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="V27" t="s">
         <v>25</v>
@@ -3499,13 +3472,13 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C28" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -3514,7 +3487,7 @@
         <v>27</v>
       </c>
       <c r="F28" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -3523,7 +3496,7 @@
         <v>3</v>
       </c>
       <c r="I28" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J28" t="s">
         <v>25</v>
@@ -3532,34 +3505,34 @@
         <v>25</v>
       </c>
       <c r="L28" t="s">
+        <v>278</v>
+      </c>
+      <c r="M28" t="s">
+        <v>279</v>
+      </c>
+      <c r="N28" t="s">
+        <v>280</v>
+      </c>
+      <c r="O28" t="s">
+        <v>281</v>
+      </c>
+      <c r="P28" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28" t="s">
+        <v>282</v>
+      </c>
+      <c r="S28" t="s">
         <v>283</v>
       </c>
-      <c r="M28" t="s">
+      <c r="T28" t="s">
+        <v>173</v>
+      </c>
+      <c r="U28" t="s">
         <v>284</v>
-      </c>
-      <c r="N28" t="s">
-        <v>285</v>
-      </c>
-      <c r="O28" t="s">
-        <v>286</v>
-      </c>
-      <c r="P28" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28" t="s">
-        <v>287</v>
-      </c>
-      <c r="S28" t="s">
-        <v>288</v>
-      </c>
-      <c r="T28" t="s">
-        <v>178</v>
-      </c>
-      <c r="U28" t="s">
-        <v>289</v>
       </c>
       <c r="V28" t="s">
         <v>25</v>
@@ -3587,30 +3560,34 @@
     <hyperlink ref="J22" r:id="rId11" xr:uid="{BFF7C92B-27D2-4305-BEDD-08F89D23D423}"/>
     <hyperlink ref="J24" r:id="rId12" xr:uid="{C4E3B51E-8486-4EF9-A741-0036D4B58361}"/>
     <hyperlink ref="O4" r:id="rId13" xr:uid="{67BB1721-3A55-464D-8B53-F6AEE62D70E2}"/>
-    <hyperlink ref="O16" r:id="rId14" xr:uid="{30FC497D-6E83-4C79-B7DB-0C3757CAA53D}"/>
-    <hyperlink ref="O20" r:id="rId15" xr:uid="{D082B78C-F77E-4053-AEFA-D29E94F2280D}"/>
-    <hyperlink ref="O21" r:id="rId16" xr:uid="{65E0E1C9-1D76-42DE-81AA-8EED3B76A436}"/>
-    <hyperlink ref="O22" r:id="rId17" xr:uid="{7DC445F4-F4D2-4997-901B-FF352B53A1EB}"/>
-    <hyperlink ref="O23" r:id="rId18" xr:uid="{AD250955-177F-42EA-88D1-4CA189383CB7}"/>
-    <hyperlink ref="O24" r:id="rId19" xr:uid="{110D1B1A-3D8C-43A4-A890-FF7EC33637FF}"/>
-    <hyperlink ref="O25" r:id="rId20" xr:uid="{9775E228-777C-4785-B8E7-E512AB9ACE7E}"/>
-    <hyperlink ref="O26" r:id="rId21" xr:uid="{3414DCE1-DDC3-479F-948D-499BCC3E2216}"/>
-    <hyperlink ref="O27" r:id="rId22" xr:uid="{AB62528D-AA7E-401E-ACCB-64AD9CEF8CF0}"/>
-    <hyperlink ref="U2" r:id="rId23" xr:uid="{6264BAB2-126F-45EE-9713-8CD2106FB8FB}"/>
-    <hyperlink ref="U3" r:id="rId24" xr:uid="{06274A1D-1E29-4B0B-B243-9C4510F45DB5}"/>
-    <hyperlink ref="O3" r:id="rId25" xr:uid="{706D8881-498A-4F80-9D1F-82FC5F1430D2}"/>
-    <hyperlink ref="U6" r:id="rId26" xr:uid="{E0DEBA59-BA3E-44A0-8189-6571C7FF2B06}"/>
-    <hyperlink ref="O6" r:id="rId27" xr:uid="{B3B5403C-1223-4818-834A-63794CF23FDC}"/>
-    <hyperlink ref="U7" r:id="rId28" xr:uid="{75ACB5B1-C877-4E39-AF14-E645458DFC40}"/>
-    <hyperlink ref="O9" r:id="rId29" xr:uid="{4C6AB3BF-9D80-4FE9-B568-C6930B9B6C26}"/>
-    <hyperlink ref="U24" r:id="rId30" xr:uid="{14B53886-7BF0-4CB4-AB87-069FC12817D9}"/>
-    <hyperlink ref="U26" r:id="rId31" xr:uid="{EC7F23C5-1491-43C3-BF80-23691E395648}"/>
-    <hyperlink ref="O13" r:id="rId32" xr:uid="{95C7B83C-FCF9-4B10-8BED-8F762C1482B4}"/>
-    <hyperlink ref="O10" r:id="rId33" xr:uid="{462A3F5D-5B23-42D6-8B88-A09792E3690E}"/>
+    <hyperlink ref="O20" r:id="rId14" xr:uid="{D082B78C-F77E-4053-AEFA-D29E94F2280D}"/>
+    <hyperlink ref="O21" r:id="rId15" xr:uid="{65E0E1C9-1D76-42DE-81AA-8EED3B76A436}"/>
+    <hyperlink ref="O22" r:id="rId16" xr:uid="{7DC445F4-F4D2-4997-901B-FF352B53A1EB}"/>
+    <hyperlink ref="O23" r:id="rId17" xr:uid="{AD250955-177F-42EA-88D1-4CA189383CB7}"/>
+    <hyperlink ref="O24" r:id="rId18" xr:uid="{110D1B1A-3D8C-43A4-A890-FF7EC33637FF}"/>
+    <hyperlink ref="O25" r:id="rId19" xr:uid="{9775E228-777C-4785-B8E7-E512AB9ACE7E}"/>
+    <hyperlink ref="O26" r:id="rId20" xr:uid="{3414DCE1-DDC3-479F-948D-499BCC3E2216}"/>
+    <hyperlink ref="O27" r:id="rId21" xr:uid="{AB62528D-AA7E-401E-ACCB-64AD9CEF8CF0}"/>
+    <hyperlink ref="U2" r:id="rId22" xr:uid="{6264BAB2-126F-45EE-9713-8CD2106FB8FB}"/>
+    <hyperlink ref="U3" r:id="rId23" xr:uid="{06274A1D-1E29-4B0B-B243-9C4510F45DB5}"/>
+    <hyperlink ref="O3" r:id="rId24" xr:uid="{706D8881-498A-4F80-9D1F-82FC5F1430D2}"/>
+    <hyperlink ref="U6" r:id="rId25" xr:uid="{E0DEBA59-BA3E-44A0-8189-6571C7FF2B06}"/>
+    <hyperlink ref="O6" r:id="rId26" xr:uid="{B3B5403C-1223-4818-834A-63794CF23FDC}"/>
+    <hyperlink ref="U7" r:id="rId27" xr:uid="{75ACB5B1-C877-4E39-AF14-E645458DFC40}"/>
+    <hyperlink ref="O9" r:id="rId28" xr:uid="{4C6AB3BF-9D80-4FE9-B568-C6930B9B6C26}"/>
+    <hyperlink ref="U24" r:id="rId29" xr:uid="{14B53886-7BF0-4CB4-AB87-069FC12817D9}"/>
+    <hyperlink ref="U26" r:id="rId30" xr:uid="{EC7F23C5-1491-43C3-BF80-23691E395648}"/>
+    <hyperlink ref="O13" r:id="rId31" xr:uid="{95C7B83C-FCF9-4B10-8BED-8F762C1482B4}"/>
+    <hyperlink ref="O10" r:id="rId32" xr:uid="{462A3F5D-5B23-42D6-8B88-A09792E3690E}"/>
+    <hyperlink ref="O7" r:id="rId33" xr:uid="{E4DF4522-29CD-4DF8-8E4C-F2E12A0FE923}"/>
+    <hyperlink ref="J16" r:id="rId34" xr:uid="{985F2B97-9E45-4E43-8852-94E6AE45C66F}"/>
+    <hyperlink ref="O16" r:id="rId35" xr:uid="{52943A91-0FD8-4CB2-9968-2FC46C5E3FDE}"/>
+    <hyperlink ref="U16" r:id="rId36" xr:uid="{16B8A05B-57AC-4A95-830A-D9B8D6529625}"/>
+    <hyperlink ref="U13" r:id="rId37" xr:uid="{EDFBC171-121B-4CED-827B-8C3E121A62AA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:X1 A28:B28 A10:N10 A2:I2 K2:T2 A3:I3 K3:N3 A4:I4 K4:N4 A5:I5 K5:X5 A6:I6 K6:N6 A7:I7 K7:T7 A8:B8 D8:M8 A9:B9 D9:N9 A13:I13 A11:I11 K11:X11 A12:I12 K12:O12 A16:N16 A14:B14 D14:I14 K14:X14 K13:N13 A15:I15 K15:X15 A18:X19 A17:I17 K17:X17 A23:N23 A21:I21 K21:N21 A22 C22:I22 K22:N22 A25:N25 A24:I24 K24:N24 A27:B27 A26:B26 K26:N26 D28:O28 D26:G26 I26 D27:G27 I27:N27 Q4:X4 Q8:X8 Q12:X12 P16:X16 A20:N20 Q20:X20 P21:X21 P22:X22 P23:X23 P24:T24 P25:X25 P26:T26 P27:X27 Q28:X28 V2:X2 V3:X3 P3:T3 V6:X6 P6:T6 V7:X7 V9:X9 P9:T9 V10:X10 V24:X24 V26:X26 P13:X13 P10:T10" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:X1 A28:B28 A10:N10 A2:I2 K2:T2 A3:I3 K3:N3 A4:I4 K4:N4 A5:I5 K5:X5 A6:I6 K6 A7:I7 K7:N7 A8:B8 D8:M8 A9:B9 D9:N9 A13:I13 A11:I11 K11:X11 A12:I12 K12:O12 A16:I16 A14:B14 D14:I14 K14:X14 K13:N13 A15:I15 K15:X15 A18:X19 A17:I17 K17:X17 A23:N23 A21:I21 K21:N21 A22 C22:I22 K22:N22 A25:N25 A24:I24 K24:N24 A27:B27 A26:B26 K26:N26 D28:O28 D26:G26 I26 D27:G27 I27:N27 Q4:X4 Q8:X8 Q12:X12 P16:T16 A20:N20 Q20:X20 P21:X21 P22:X22 P23:X23 P24:T24 P25:X25 P26:T26 P27:T27 Q28:X28 V2:X2 V3:X3 P3:T3 V6:X6 P6:T6 V7:X7 V9:X9 P9:T9 V10:X10 V24:X24 V26:X26 P13:T13 P10:T10 P7:T7 K16:N16 V16:X16 V13:X13 V27:X27" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3622,15 +3599,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
@@ -3638,15 +3615,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B4">
         <v>29</v>
@@ -3654,10 +3631,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B5" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>

--- a/docs/eval/golden-set.xlsx
+++ b/docs/eval/golden-set.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerom\ConferenceFinder\docs\eval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0045FB-F638-4026-BFDE-7740EB6AE98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857218AD-37DD-476C-BCD9-4D756CEA72A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="golden" sheetId="1" r:id="rId1"/>
@@ -2018,7 +2018,7 @@
         <v>87</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>5</v>
@@ -2756,7 +2756,7 @@
         <v>87</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18">
         <v>4</v>
@@ -3587,7 +3587,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:X1 A28:B28 A10:N10 A2:I2 K2:T2 A3:I3 K3:N3 A4:I4 K4:N4 A5:I5 K5:X5 A6:I6 K6 A7:I7 K7:N7 A8:B8 D8:M8 A9:B9 D9:N9 A13:I13 A11:I11 K11:X11 A12:I12 K12:O12 A16:I16 A14:B14 D14:I14 K14:X14 K13:N13 A15:I15 K15:X15 A18:X19 A17:I17 K17:X17 A23:N23 A21:I21 K21:N21 A22 C22:I22 K22:N22 A25:N25 A24:I24 K24:N24 A27:B27 A26:B26 K26:N26 D28:O28 D26:G26 I26 D27:G27 I27:N27 Q4:X4 Q8:X8 Q12:X12 P16:T16 A20:N20 Q20:X20 P21:X21 P22:X22 P23:X23 P24:T24 P25:X25 P26:T26 P27:T27 Q28:X28 V2:X2 V3:X3 P3:T3 V6:X6 P6:T6 V7:X7 V9:X9 P9:T9 V10:X10 V24:X24 V26:X26 P13:T13 P10:T10 P7:T7 K16:N16 V16:X16 V13:X13 V27:X27" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:X1 A28:B28 A10:N10 A2:I2 K2:T2 A3:I3 K3:N3 A4:I4 K4:N4 A5:I5 K5:X5 A6:I6 K6 A7:I7 K7:N7 A8:B8 D8:F8 A9:B9 D9:N9 A13:I13 A11:I11 K11:X11 A12:I12 K12:O12 A16:I16 A14:B14 D14:I14 K14:X14 K13:N13 A15:I15 K15:X15 A19:X19 A17:I17 K17:X17 A23:N23 A21:I21 K21:N21 A22 C22:I22 K22:N22 A25:N25 A24:I24 K24:N24 A27:B27 A26:B26 K26:N26 D28:O28 D26:G26 I26 D27:G27 I27:N27 Q4:X4 Q8:X8 Q12:X12 P16:T16 A20:N20 Q20:X20 P21:X21 P22:X22 P23:X23 P24:T24 P25:X25 P26:T26 P27:T27 Q28:X28 V2:X2 V3:X3 P3:T3 V6:X6 P6:T6 V7:X7 V9:X9 P9:T9 V10:X10 V24:X24 V26:X26 P13:T13 P10:T10 P7:T7 K16:N16 V16:X16 V13:X13 V27:X27 H8:M8 A18:F18 H18:X18" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
